--- a/11_MaxPID/11_MaxPID_Corrige.xlsx
+++ b/11_MaxPID/11_MaxPID_Corrige.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\TP_Corriges\11_MaxPID\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C46EF7EF-EBD9-46C1-AACE-27F72689CDE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1833EE05-EC19-45C9-A8C5-84A417E3692A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{823A92E8-CAB8-459A-AA21-5E852254C47E}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="19420" windowHeight="10300" xr2:uid="{823A92E8-CAB8-459A-AA21-5E852254C47E}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -791,7 +791,7 @@
   <cols>
     <col min="1" max="1" width="15.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="11.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
@@ -949,7 +949,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="26" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" ht="26" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>14</v>
       </c>
@@ -965,7 +965,7 @@
         <v>0.13302294645826404</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>15</v>
       </c>
@@ -981,7 +981,7 @@
         <v>0.46291985367475891</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="39" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" ht="39" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>16</v>
       </c>
@@ -997,7 +997,7 @@
         <v>0.40405719986697708</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>15</v>
       </c>
@@ -1005,18 +1005,21 @@
         <f>SUM(D20:D22)</f>
         <v>1.5034999999999999E-5</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" ht="39" x14ac:dyDescent="0.35">
+      <c r="G23">
+        <v>1.5034999999999999E-5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="39" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>18</v>
       </c>
